--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D316"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6120,6 +6120,24 @@
       <c r="D316" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="C317" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9797,6 +9815,16 @@
       </c>
       <c r="B366" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -9965,28 +9993,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2659950372297006</v>
+        <v>0.2612454470639866</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.185867020155787</v>
+        <v>0.1799485142845785</v>
       </c>
       <c r="M2" t="n">
-        <v>3.132591965212598</v>
+        <v>3.144491414101358</v>
       </c>
       <c r="N2" t="n">
-        <v>15.99521780867353</v>
+        <v>16.11279870876386</v>
       </c>
       <c r="O2" t="n">
-        <v>3.999402181410808</v>
+        <v>4.014075075128001</v>
       </c>
       <c r="P2" t="n">
-        <v>350.7949595879193</v>
+        <v>350.8457905644888</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10047,28 +10075,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2641048679362729</v>
+        <v>0.2619743057417639</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1968086643014328</v>
+        <v>0.1949839801110269</v>
       </c>
       <c r="M3" t="n">
-        <v>2.83074339071884</v>
+        <v>2.830974952676788</v>
       </c>
       <c r="N3" t="n">
-        <v>14.69189081300622</v>
+        <v>14.67924281644652</v>
       </c>
       <c r="O3" t="n">
-        <v>3.83300023649963</v>
+        <v>3.831349999210007</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4151265899271</v>
+        <v>346.4379282534833</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10106,7 +10134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D316"/>
+  <dimension ref="A1:D317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17061,6 +17089,28 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.51151631007139,174.47752234647092</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.51165684051162,174.47840396883163</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6136,6 +6136,24 @@
         <v>350.05</v>
       </c>
       <c r="D317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="C318" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="D318" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6152,7 +6170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9825,6 +9843,16 @@
       </c>
       <c r="B367" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -9993,28 +10021,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2612454470639866</v>
+        <v>0.2562638869994288</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1799485142845785</v>
+        <v>0.1736873858933825</v>
       </c>
       <c r="M2" t="n">
-        <v>3.144491414101358</v>
+        <v>3.158131101245087</v>
       </c>
       <c r="N2" t="n">
-        <v>16.11279870876386</v>
+        <v>16.24710938711021</v>
       </c>
       <c r="O2" t="n">
-        <v>4.014075075128001</v>
+        <v>4.03077032180081</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8457905644888</v>
+        <v>350.8993032750891</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10075,28 +10103,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2619743057417639</v>
+        <v>0.2603303301043469</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1949839801110269</v>
+        <v>0.193884287559135</v>
       </c>
       <c r="M3" t="n">
-        <v>2.830974952676788</v>
+        <v>2.829073616394426</v>
       </c>
       <c r="N3" t="n">
-        <v>14.67924281644652</v>
+        <v>14.65309926148634</v>
       </c>
       <c r="O3" t="n">
-        <v>3.831349999210007</v>
+        <v>3.827936684623499</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4379282534833</v>
+        <v>346.4555881012778</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10134,7 +10162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17111,6 +17139,28 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.51152012435482,174.47752150173147</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.51165036509525,174.47840540287987</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6156,6 +6156,24 @@
       <c r="D318" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="C319" t="n">
+        <v>354.15</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9853,6 +9871,16 @@
       </c>
       <c r="B368" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -10021,28 +10049,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2562638869994288</v>
+        <v>0.25440945106523</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1736873858933825</v>
+        <v>0.1724040549387101</v>
       </c>
       <c r="M2" t="n">
-        <v>3.158131101245087</v>
+        <v>3.156779393909435</v>
       </c>
       <c r="N2" t="n">
-        <v>16.24710938711021</v>
+        <v>16.22118081146655</v>
       </c>
       <c r="O2" t="n">
-        <v>4.03077032180081</v>
+        <v>4.027552707472188</v>
       </c>
       <c r="P2" t="n">
-        <v>350.8993032750891</v>
+        <v>350.9193880076771</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10103,28 +10131,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2603303301043469</v>
+        <v>0.2608499721169282</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.193884287559135</v>
+        <v>0.1956034532563398</v>
       </c>
       <c r="M3" t="n">
-        <v>2.829073616394426</v>
+        <v>2.822949903996093</v>
       </c>
       <c r="N3" t="n">
-        <v>14.65309926148634</v>
+        <v>14.60899614958347</v>
       </c>
       <c r="O3" t="n">
-        <v>3.827936684623499</v>
+        <v>3.822171653600015</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4555881012778</v>
+        <v>346.4499600444269</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10162,7 +10190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D318"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17161,6 +17189,28 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.51147728019421,174.47753099031226</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.511620471734425,174.47841202307254</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6174,6 +6174,42 @@
       <c r="D319" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>353.49</v>
+      </c>
+      <c r="C320" t="n">
+        <v>351.99</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>352.26</v>
+      </c>
+      <c r="C321" t="n">
+        <v>351.74</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B369"/>
+  <dimension ref="A1:B371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9881,6 +9917,26 @@
       </c>
       <c r="B369" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -10049,28 +10105,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25440945106523</v>
+        <v>0.2481729094476438</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1724040549387101</v>
+        <v>0.1661813188588862</v>
       </c>
       <c r="M2" t="n">
-        <v>3.156779393909435</v>
+        <v>3.165333302062715</v>
       </c>
       <c r="N2" t="n">
-        <v>16.22118081146655</v>
+        <v>16.26421429889128</v>
       </c>
       <c r="O2" t="n">
-        <v>4.027552707472188</v>
+        <v>4.032891555558032</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9193880076771</v>
+        <v>350.9873278486491</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10131,28 +10187,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2608499721169282</v>
+        <v>0.2588669843180558</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1956034532563398</v>
+        <v>0.1952963592603074</v>
       </c>
       <c r="M3" t="n">
-        <v>2.822949903996093</v>
+        <v>2.81367822274148</v>
       </c>
       <c r="N3" t="n">
-        <v>14.60899614958347</v>
+        <v>14.53215668742413</v>
       </c>
       <c r="O3" t="n">
-        <v>3.822171653600015</v>
+        <v>3.812106594446715</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4499600444269</v>
+        <v>346.4715619657565</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10190,7 +10246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17211,6 +17267,50 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.51148925527023,174.4775283382254</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.51163963187078,174.47840777986352</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.511500165895,174.47752592187896</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.511641849479155,174.47840728875124</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0085/nzd0085.xlsx
+++ b/data/nzd0085/nzd0085.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6208,6 +6208,42 @@
         <v>351.74</v>
       </c>
       <c r="D321" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="C322" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="C323" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="D323" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6224,7 +6260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B371"/>
+  <dimension ref="A1:B373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9937,6 +9973,26 @@
       </c>
       <c r="B371" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -10105,28 +10161,28 @@
         <v>0.0902</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2481729094476438</v>
+        <v>0.2443441895625809</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1661813188588862</v>
+        <v>0.1633857114999355</v>
       </c>
       <c r="M2" t="n">
-        <v>3.165333302062715</v>
+        <v>3.162786606585803</v>
       </c>
       <c r="N2" t="n">
-        <v>16.26421429889128</v>
+        <v>16.21775345666307</v>
       </c>
       <c r="O2" t="n">
-        <v>4.032891555558032</v>
+        <v>4.027127196484247</v>
       </c>
       <c r="P2" t="n">
-        <v>350.9873278486491</v>
+        <v>351.0291822714089</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10187,28 +10243,28 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2588669843180558</v>
+        <v>0.2549268643412421</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1952963592603074</v>
+        <v>0.1919908987434225</v>
       </c>
       <c r="M3" t="n">
-        <v>2.81367822274148</v>
+        <v>2.812773828448631</v>
       </c>
       <c r="N3" t="n">
-        <v>14.53215668742413</v>
+        <v>14.50916023764422</v>
       </c>
       <c r="O3" t="n">
-        <v>3.812106594446715</v>
+        <v>3.809089161157063</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4715619657565</v>
+        <v>346.5146418793436</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10246,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D321"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17311,6 +17367,50 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.511479231688085,174.4775305581204</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.51164362356583,174.4784068958614</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.511479231688085,174.4775305581204</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.51166553353635,174.47840204367063</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
